--- a/2-Data_Analysis/EDA/EDA_Datos_necesarios.xlsx
+++ b/2-Data_Analysis/EDA/EDA_Datos_necesarios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NaiaJon\Documents\Naia\BootcampDataScience\2026-02-BILBAO-FT-Data-Science\2-Data_Analysis\EDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CACDB524-EE8E-460A-A8C8-D37E2AF070B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F76A18CF-F31F-41AF-AEEB-7326EE39FE32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{586EFF4D-576F-452D-B573-AABBE52372BE}"/>
+    <workbookView xWindow="3680" yWindow="1900" windowWidth="14400" windowHeight="7270" xr2:uid="{586EFF4D-576F-452D-B573-AABBE52372BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Vivienda" sheetId="1" r:id="rId1"/>
@@ -136,7 +136,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -148,6 +148,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -176,18 +184,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -520,7 +528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13B23A18-5B61-4DBC-99D4-797C43F12B35}">
-  <dimension ref="A2:H9"/>
+  <dimension ref="A2:E9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.453125" customWidth="1"/>
@@ -530,19 +538,16 @@
     <col min="5" max="5" width="26.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-    </row>
-    <row r="3" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -555,11 +560,11 @@
       <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -576,7 +581,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -593,7 +598,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -610,7 +615,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -621,12 +626,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -638,7 +643,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73F2DFAE-D966-4B66-ABBB-3D5C93C0662E}">
-  <dimension ref="A3:H7"/>
+  <dimension ref="A3:F7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="41.453125" customWidth="1"/>
@@ -647,19 +652,16 @@
     <col min="4" max="4" width="20.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-    </row>
-    <row r="4" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -672,11 +674,11 @@
       <c r="D4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -693,7 +695,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -707,7 +709,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -717,11 +719,14 @@
       <c r="C7" t="s">
         <v>29</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="3" t="s">
         <v>28</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F7" r:id="rId1" xr:uid="{07BB742F-D63A-4B43-BCDC-C1BC728654BE}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
